--- a/MotorDriver1/jlcpcb/production_files_final/CPL-MotorDriver1.xlsx
+++ b/MotorDriver1/jlcpcb/production_files_final/CPL-MotorDriver1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emma/Documents/JHU/Capstone_Smart_Saddle_Pad/MotorDriver1/jlcpcb/production_files_final/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28BDF1DE-78C0-8A44-AEFE-12791FCA83A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD99E87-A1D4-054B-B258-516DEC25124B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{07E7F4AD-9A9B-9243-8861-09B9D84CB710}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="35840" windowHeight="22400" xr2:uid="{07E7F4AD-9A9B-9243-8861-09B9D84CB710}"/>
   </bookViews>
   <sheets>
     <sheet name="CPL-MotorDriver1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="104">
   <si>
     <t>Designator</t>
   </si>
@@ -323,6 +323,15 @@
   </si>
   <si>
     <t>D8_TEX</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>MINISMDC260F/16-2</t>
+  </si>
+  <si>
+    <t>Fuse_1812_4532Metric</t>
   </si>
 </sst>
 </file>
@@ -1190,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{906039C1-864D-F645-ABB3-7F5684404EDD}">
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -1561,7 +1570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -1584,7 +1593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1607,7 +1616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1630,7 +1639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -1653,7 +1662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>37</v>
       </c>
@@ -1676,7 +1685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>39</v>
       </c>
@@ -1699,7 +1708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1722,7 +1731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -1745,7 +1754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -1768,7 +1777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -1791,7 +1800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -1814,7 +1823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>49</v>
       </c>
@@ -1837,7 +1846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -1860,70 +1869,71 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" s="1">
+        <v>177.5</v>
+      </c>
+      <c r="E30" s="1">
+        <v>-78.099999999999994</v>
+      </c>
+      <c r="F30" s="1">
+        <v>180</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>51</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>52</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>53</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <v>152</v>
       </c>
-      <c r="E30">
+      <c r="E31">
         <v>-93.5</v>
       </c>
-      <c r="F30">
+      <c r="F31">
         <v>0</v>
       </c>
-      <c r="G30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>54</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>55</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>56</v>
       </c>
-      <c r="D31">
+      <c r="D32">
         <v>125.6066</v>
       </c>
-      <c r="E31">
+      <c r="E32">
         <v>-109.737899</v>
       </c>
-      <c r="F31">
+      <c r="F32">
         <v>-90</v>
-      </c>
-      <c r="G31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32">
-        <v>130</v>
-      </c>
-      <c r="E32">
-        <v>-66.5</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
       </c>
       <c r="G32" t="s">
         <v>10</v>
@@ -1931,7 +1941,7 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -1940,7 +1950,7 @@
         <v>59</v>
       </c>
       <c r="D33">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E33">
         <v>-66.5</v>
@@ -1954,7 +1964,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
         <v>58</v>
@@ -1963,13 +1973,13 @@
         <v>59</v>
       </c>
       <c r="D34">
-        <v>171.5</v>
+        <v>146</v>
       </c>
       <c r="E34">
-        <v>-88.18</v>
+        <v>-66.5</v>
       </c>
       <c r="F34">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G34" t="s">
         <v>10</v>
@@ -1977,7 +1987,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
         <v>58</v>
@@ -1986,10 +1996,10 @@
         <v>59</v>
       </c>
       <c r="D35">
-        <v>171.4666</v>
+        <v>171.5</v>
       </c>
       <c r="E35">
-        <v>-115</v>
+        <v>-88.18</v>
       </c>
       <c r="F35">
         <v>-90</v>
@@ -2000,22 +2010,22 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C36" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D36">
-        <v>125.6568</v>
+        <v>171.4666</v>
       </c>
       <c r="E36">
-        <v>-72.976600000000005</v>
+        <v>-115</v>
       </c>
       <c r="F36">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G36" t="s">
         <v>10</v>
@@ -2023,7 +2033,7 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
         <v>64</v>
@@ -2032,13 +2042,13 @@
         <v>65</v>
       </c>
       <c r="D37">
-        <v>163</v>
+        <v>125.6568</v>
       </c>
       <c r="E37">
-        <v>-100.31</v>
+        <v>-72.976600000000005</v>
       </c>
       <c r="F37">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G37" t="s">
         <v>10</v>
@@ -2046,19 +2056,19 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C38" t="s">
         <v>65</v>
       </c>
       <c r="D38">
-        <v>130.2122</v>
+        <v>163</v>
       </c>
       <c r="E38">
-        <v>-107.737899</v>
+        <v>-100.31</v>
       </c>
       <c r="F38">
         <v>-90</v>
@@ -2069,7 +2079,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B39" t="s">
         <v>68</v>
@@ -2078,13 +2088,13 @@
         <v>65</v>
       </c>
       <c r="D39">
-        <v>131.0838</v>
+        <v>130.2122</v>
       </c>
       <c r="E39">
-        <v>-111.737899</v>
+        <v>-107.737899</v>
       </c>
       <c r="F39">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G39" t="s">
         <v>10</v>
@@ -2092,22 +2102,22 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
         <v>65</v>
       </c>
       <c r="D40">
-        <v>159.5</v>
+        <v>131.0838</v>
       </c>
       <c r="E40">
-        <v>-116</v>
+        <v>-111.737899</v>
       </c>
       <c r="F40">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G40" t="s">
         <v>10</v>
@@ -2115,7 +2125,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
         <v>64</v>
@@ -2124,10 +2134,10 @@
         <v>65</v>
       </c>
       <c r="D41">
-        <v>146.5</v>
+        <v>159.5</v>
       </c>
       <c r="E41">
-        <v>-115.62690000000001</v>
+        <v>-116</v>
       </c>
       <c r="F41">
         <v>-90</v>
@@ -2138,19 +2148,19 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C42" t="s">
         <v>65</v>
       </c>
       <c r="D42">
-        <v>159.5</v>
+        <v>146.5</v>
       </c>
       <c r="E42">
-        <v>-118.49</v>
+        <v>-115.62690000000001</v>
       </c>
       <c r="F42">
         <v>-90</v>
@@ -2161,7 +2171,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
         <v>73</v>
@@ -2170,10 +2180,10 @@
         <v>65</v>
       </c>
       <c r="D43">
-        <v>146.5</v>
+        <v>159.5</v>
       </c>
       <c r="E43">
-        <v>-117.8721</v>
+        <v>-118.49</v>
       </c>
       <c r="F43">
         <v>-90</v>
@@ -2184,22 +2194,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B44" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
         <v>65</v>
       </c>
       <c r="D44">
-        <v>165.02340000000001</v>
+        <v>146.5</v>
       </c>
       <c r="E44">
-        <v>-84.18</v>
+        <v>-117.8721</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G44" t="s">
         <v>10</v>
@@ -2207,7 +2217,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B45" t="s">
         <v>64</v>
@@ -2216,10 +2226,10 @@
         <v>65</v>
       </c>
       <c r="D45">
-        <v>154.11840000000001</v>
+        <v>165.02340000000001</v>
       </c>
       <c r="E45">
-        <v>-77.364999999999995</v>
+        <v>-84.18</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2230,19 +2240,19 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>77</v>
-      </c>
-      <c r="B46">
-        <v>120</v>
+        <v>76</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
       </c>
       <c r="C46" t="s">
         <v>65</v>
       </c>
       <c r="D46">
-        <v>161.76</v>
+        <v>154.11840000000001</v>
       </c>
       <c r="E46">
-        <v>-83.5</v>
+        <v>-77.364999999999995</v>
       </c>
       <c r="F46">
         <v>0</v>
@@ -2253,7 +2263,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B47">
         <v>120</v>
@@ -2262,13 +2272,13 @@
         <v>65</v>
       </c>
       <c r="D47">
-        <v>153.52500000000001</v>
+        <v>161.76</v>
       </c>
       <c r="E47">
-        <v>-79.364999999999995</v>
+        <v>-83.5</v>
       </c>
       <c r="F47">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G47" t="s">
         <v>10</v>
@@ -2276,19 +2286,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>79</v>
-      </c>
-      <c r="B48" t="s">
-        <v>64</v>
+        <v>78</v>
+      </c>
+      <c r="B48">
+        <v>120</v>
       </c>
       <c r="C48" t="s">
         <v>65</v>
       </c>
       <c r="D48">
-        <v>166.5</v>
+        <v>153.52500000000001</v>
       </c>
       <c r="E48">
-        <v>-77.989999999999995</v>
+        <v>-79.364999999999995</v>
       </c>
       <c r="F48">
         <v>-90</v>
@@ -2299,19 +2309,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>80</v>
-      </c>
-      <c r="B49">
-        <v>1</v>
+        <v>79</v>
+      </c>
+      <c r="B49" t="s">
+        <v>64</v>
       </c>
       <c r="C49" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D49">
-        <v>135</v>
+        <v>166.5</v>
       </c>
       <c r="E49">
-        <v>-72.976600000000005</v>
+        <v>-77.989999999999995</v>
       </c>
       <c r="F49">
         <v>-90</v>
@@ -2322,7 +2332,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -2331,13 +2341,13 @@
         <v>81</v>
       </c>
       <c r="D50">
-        <v>165.0334</v>
+        <v>135</v>
       </c>
       <c r="E50">
-        <v>-94</v>
+        <v>-72.976600000000005</v>
       </c>
       <c r="F50">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G50" t="s">
         <v>10</v>
@@ -2345,22 +2355,22 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>83</v>
-      </c>
-      <c r="B51" t="s">
-        <v>64</v>
+        <v>82</v>
+      </c>
+      <c r="B51">
+        <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D51">
-        <v>141.82839999999999</v>
+        <v>165.0334</v>
       </c>
       <c r="E51">
-        <v>-72.976600000000005</v>
+        <v>-94</v>
       </c>
       <c r="F51">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G51" t="s">
         <v>10</v>
@@ -2368,7 +2378,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B52" t="s">
         <v>64</v>
@@ -2377,13 +2387,13 @@
         <v>65</v>
       </c>
       <c r="D52">
-        <v>164.83869999999999</v>
+        <v>141.82839999999999</v>
       </c>
       <c r="E52">
-        <v>-110.63160000000001</v>
+        <v>-72.976600000000005</v>
       </c>
       <c r="F52">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G52" t="s">
         <v>10</v>
@@ -2391,22 +2401,22 @@
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>85</v>
-      </c>
-      <c r="B53">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="B53" t="s">
+        <v>64</v>
       </c>
       <c r="C53" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="D53">
-        <v>151.5</v>
+        <v>164.83869999999999</v>
       </c>
       <c r="E53">
-        <v>-73</v>
+        <v>-110.63160000000001</v>
       </c>
       <c r="F53">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -2414,7 +2424,7 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -2423,13 +2433,13 @@
         <v>81</v>
       </c>
       <c r="D54">
-        <v>164.83869999999999</v>
+        <v>151.5</v>
       </c>
       <c r="E54">
-        <v>-120.5</v>
+        <v>-73</v>
       </c>
       <c r="F54">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G54" t="s">
         <v>10</v>
@@ -2437,22 +2447,22 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>87</v>
-      </c>
-      <c r="B55" t="s">
-        <v>64</v>
+        <v>86</v>
+      </c>
+      <c r="B55">
+        <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="D55">
-        <v>128.4</v>
+        <v>164.83869999999999</v>
       </c>
       <c r="E55">
-        <v>-81.489999999999995</v>
+        <v>-120.5</v>
       </c>
       <c r="F55">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G55" t="s">
         <v>10</v>
@@ -2460,22 +2470,22 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B56" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="C56" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="D56">
-        <v>125</v>
+        <v>128.4</v>
       </c>
       <c r="E56">
-        <v>-86</v>
+        <v>-81.489999999999995</v>
       </c>
       <c r="F56">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G56" t="s">
         <v>10</v>
@@ -2483,7 +2493,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B57" t="s">
         <v>89</v>
@@ -2492,10 +2502,10 @@
         <v>89</v>
       </c>
       <c r="D57">
-        <v>125.1</v>
+        <v>125</v>
       </c>
       <c r="E57">
-        <v>-97</v>
+        <v>-86</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -2506,7 +2516,7 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B58" t="s">
         <v>89</v>
@@ -2515,13 +2525,13 @@
         <v>89</v>
       </c>
       <c r="D58">
-        <v>170</v>
+        <v>125.1</v>
       </c>
       <c r="E58">
-        <v>-101.5</v>
+        <v>-97</v>
       </c>
       <c r="F58">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G58" t="s">
         <v>10</v>
@@ -2529,22 +2539,22 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C59" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D59">
-        <v>137.5</v>
+        <v>170</v>
       </c>
       <c r="E59">
-        <v>-114.5</v>
+        <v>-101.5</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G59" t="s">
         <v>10</v>
@@ -2552,22 +2562,22 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C60" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D60">
-        <v>139.5</v>
+        <v>137.5</v>
       </c>
       <c r="E60">
-        <v>-106.8875</v>
+        <v>-114.5</v>
       </c>
       <c r="F60">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G60" t="s">
         <v>10</v>
@@ -2575,24 +2585,47 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>95</v>
+      </c>
+      <c r="B61" t="s">
+        <v>96</v>
+      </c>
+      <c r="C61" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61">
+        <v>139.5</v>
+      </c>
+      <c r="E61">
+        <v>-106.8875</v>
+      </c>
+      <c r="F61">
+        <v>90</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
         <v>98</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>99</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>100</v>
       </c>
-      <c r="D61">
+      <c r="D62">
         <v>153</v>
       </c>
-      <c r="E61">
+      <c r="E62">
         <v>-116</v>
       </c>
-      <c r="F61">
+      <c r="F62">
         <v>0</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G62" t="s">
         <v>10</v>
       </c>
     </row>
